--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569797092</v>
+        <v>46157.93104046598</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93104046598</v>
+        <v>46157.93175587073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93175587073</v>
+        <v>46157.93401373032</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401373032</v>
+        <v>46157.93719358561</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719358561</v>
+        <v>46158.28217534625</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217534625</v>
+        <v>46158.29683382739</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29683382739</v>
+        <v>46158.29816257142</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29816257142</v>
+        <v>46158.33388581871</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388581871</v>
+        <v>46158.36858391186</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858391186</v>
+        <v>46158.37289073003</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
